--- a/public/assets/import-templates/import-employees-template.xlsx
+++ b/public/assets/import-templates/import-employees-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mjd\mujdn-frontend\public\assets\import-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\attendnace-project\3p-attend-front\public\assets\import-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1F8DD7-F3ED-4112-A405-46308C046868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53085D3-1CD8-45F5-ADA7-7CD182C16CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>FullNameAr</t>
   </si>
   <si>
-    <t>NationalId</t>
-  </si>
-  <si>
     <t>PhoneNumber</t>
   </si>
   <si>
@@ -65,6 +62,9 @@
   </si>
   <si>
     <t>JoinDate (mm/dd/yyyy)</t>
+  </si>
+  <si>
+    <t>EmployeeCode</t>
   </si>
 </sst>
 </file>
@@ -433,7 +433,7 @@
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="3" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" customWidth="1"/>
@@ -460,37 +460,37 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/import-templates/import-employees-template.xlsx
+++ b/public/assets/import-templates/import-employees-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\attendnace-project\3p-attend-front\public\assets\import-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53085D3-1CD8-45F5-ADA7-7CD182C16CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8573BA46-38F0-4D06-BD24-E7F0DA47F80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <t>JoinDate (mm/dd/yyyy)</t>
   </si>
   <si>
-    <t>EmployeeCode</t>
+    <t>EmployeeCode (xxxxxx)</t>
   </si>
 </sst>
 </file>
@@ -433,7 +433,7 @@
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="3" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" customWidth="1"/>
